--- a/job_application_forms/019_fintech_role_aptitude_exam--job_application_forms.xlsx
+++ b/job_application_forms/019_fintech_role_aptitude_exam--job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>candidate_name</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>What is your email address?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>experience</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>How many years of experience do you have in the fintech industry?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>programming_languages</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>What programming languages are you proficient in?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>job_role</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>What is your current job role?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>What is your current company?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>expected_salary</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>What is your expected salary range?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>education</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>What is your highest level of education?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>field_of_interest</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>What is your field of interest in fintech?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_8</t>
+          <t>area_of_expertise</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>question_8</t>
+          <t>What is your area of expertise in fintech?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_9</t>
+          <t>experience_with_tools</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>question_9</t>
+          <t>Can you describe your experience with fintech tools?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_10</t>
+          <t>knowledge_of_fintech</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>question_10</t>
+          <t>How would you rate your knowledge of fintech?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question_11</t>
+          <t>fintech_project</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>question_11</t>
+          <t>Can you give an example of a fintech project you worked on?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question_12</t>
+          <t>experience_with_analysis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>question_12</t>
+          <t>Can you describe your experience with data analysis?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question_13</t>
+          <t>financial_modeling</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>question_13</t>
+          <t>Can you explain the concept of financial modeling?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>question_14</t>
+          <t>company_example</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>question_14</t>
+          <t>Can you give an example of a fintech company you worked with?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>question_15</t>
+          <t>fintech_concept</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>question_15</t>
+          <t>Can you describe your experience with AI and machine learning?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>question_16</t>
+          <t>blockchain</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>question_16</t>
+          <t>Can you explain the concept of blockchain?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>question_17</t>
+          <t>fintech_regulations</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>question_17</t>
+          <t>Can you explain the concept of fintech regulations?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,17 +952,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>question_18</t>
+          <t>fintech_article</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>question_18</t>
+          <t>Can you give an example of a fintech-related article you read?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,17 +975,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>question_19</t>
+          <t>innovation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>question_19</t>
+          <t>Can you describe your experience with fintech innovation?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -998,17 +998,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>question_20</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>question_20</t>
+          <t>Can you give an example of a fintech event you attended?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1021,17 +1021,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>question_21</t>
+          <t>book</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>question_21</t>
+          <t>Can you describe your experience with fintech-related books?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1044,17 +1044,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>question_22</t>
+          <t>research</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>question_22</t>
+          <t>Can you give an example of a fintech research paper you read?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1067,17 +1067,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>question_23</t>
+          <t>course</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>question_23</t>
+          <t>Can you describe your experience with fintech-related courses?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1090,17 +1090,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>question_24</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>question_24</t>
+          <t>Can you explain the concept of fintech trends?</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1113,17 +1113,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>question_25</t>
+          <t>trend_example</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>question_25</t>
+          <t>Can you give an example of a fintech trend you follow?</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1136,17 +1136,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>question_26</t>
+          <t>news</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>question_26</t>
+          <t>Can you describe your experience with fintech-related news sources?</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1159,17 +1159,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>question_27</t>
+          <t>question_29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>question_27</t>
+          <t>Question 29</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>submission</t>
+          <t>question_30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>submission</t>
+          <t>Question 30</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>expected_salary_2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Expected Salary 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>submission_status</t>
+          <t>Submission Status</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1251,17 +1251,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>submitted_on</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>submitted_on</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1279,154 +1279,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>submission</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>Submission</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>submission_status</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>submission_status</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>submission_status</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>submission_status</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>submitted</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>submitted</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1443,12 +1305,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1471,143 +1333,143 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>programming_languages_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Python</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>programming_languages_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>java</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Java</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>programming_languages_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>JavaScript</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>programming_languages_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>c++</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>C++</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>programming_languages_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>SQL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>programming_languages_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>c#</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>C#</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>submission_status_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>submission_status_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>submitted_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1624,7 +1486,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>submitted_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1633,958 +1495,6 @@
         </is>
       </c>
       <c r="C11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>question_6_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>question_6_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>question_7_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>question_7_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>question_8_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>question_8_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>question_9_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>question_9_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>question_10_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>question_10_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>question_11_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>question_11_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>question_12_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>question_12_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>question_13_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>question_13_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>question_14_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>question_14_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>question_15_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>question_15_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>question_16_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>question_16_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>question_17_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>question_17_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>question_18_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>question_18_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>question_19_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>question_19_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>question_21_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>question_21_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>question_22_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>question_22_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>question_24_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>question_24_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>question_25_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>question_25_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>question_26_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>question_26_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>question_27_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>question_27_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>submission_status_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>submission_status_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>submission_status_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>submission_status_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>submission_status_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>submission_status_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>submitted_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>submitted_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
         <is>
           <t>No</t>
         </is>
